--- a/data/employees.xlsx
+++ b/data/employees.xlsx
@@ -524,7 +524,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Working</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="J2" t="n">

--- a/data/employees.xlsx
+++ b/data/employees.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:L5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -484,6 +484,11 @@
           <t>current_project</t>
         </is>
       </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>emergency_number</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -535,6 +540,165 @@
           <t>santparampra.in</t>
         </is>
       </c>
+      <c r="L2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kiran</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>EMP02</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Development</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Intern</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>kiranglawe18@gmail.com</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>9766148444</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>8000</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Dadhboard</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>9766148444</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Sarthak</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>EMP03</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Development</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Intern</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>sarthak@gmail.com</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>1234567890</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Renora Ai</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Mahesh</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>EMP04</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Development</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Intern</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Mahesh@gmail.com</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>1234567890</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Inactive</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/employees.xlsx
+++ b/data/employees.xlsx
@@ -568,12 +568,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>kiranglawe18@gmail.com</t>
+          <t>kiran@gmail.com</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>9766148444</t>
+          <t>123</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -596,7 +596,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>9766148444</t>
+          <t>456</t>
         </is>
       </c>
     </row>

--- a/data/employees.xlsx
+++ b/data/employees.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L5"/>
+  <dimension ref="A1:M5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -489,6 +489,11 @@
           <t>emergency_number</t>
         </is>
       </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>emergency_contact_name</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -541,6 +546,7 @@
         </is>
       </c>
       <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -568,12 +574,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>kiran@gmail.com</t>
+          <t>kiranaglawe18@gmail.com</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>9766148444</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -596,7 +602,12 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>456</t>
+          <t>9766148444</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>Kiran</t>
         </is>
       </c>
     </row>
@@ -651,6 +662,7 @@
         </is>
       </c>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -699,6 +711,7 @@
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/employees.xlsx
+++ b/data/employees.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:J1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -479,239 +479,6 @@
           <t>salary</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>current_project</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>emergency_number</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>emergency_contact_name</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Avinash</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>EMP01</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Development</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Intern</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>avinash@gmail.com</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
-        <v>1234567890</v>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="J2" t="n">
-        <v>8000</v>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>santparampra.in</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>2</v>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Kiran</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>EMP02</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Development</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Intern</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>kiranaglawe18@gmail.com</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>9766148444</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>2026-08-01</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="J3" t="n">
-        <v>8000</v>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>Dadhboard</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>9766148444</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>Kiran</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>3</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Sarthak</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>EMP03</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Development</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Intern</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>sarthak@gmail.com</t>
-        </is>
-      </c>
-      <c r="G4" t="n">
-        <v>1234567890</v>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>2026-07-21</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="J4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>Renora Ai</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>4</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Mahesh</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>EMP04</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Development</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Intern</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Mahesh@gmail.com</t>
-        </is>
-      </c>
-      <c r="G5" t="n">
-        <v>1234567890</v>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>2026-07-20</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>Inactive</t>
-        </is>
-      </c>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/employees.xlsx
+++ b/data/employees.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J1"/>
+  <dimension ref="A1:J2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -478,6 +478,52 @@
         <is>
           <t>salary</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kiran</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>EMP01</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Development</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Intern</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>kiranaglawe18@gmail.com</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>9766148444</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
+        <v>8000</v>
       </c>
     </row>
   </sheetData>

--- a/data/employees.xlsx
+++ b/data/employees.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:J1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -478,52 +478,6 @@
         <is>
           <t>salary</t>
         </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Kiran</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>EMP01</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Development</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Intern</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>kiranaglawe18@gmail.com</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
-        <v>9766148444</v>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="J2" t="n">
-        <v>8000</v>
       </c>
     </row>
   </sheetData>

--- a/data/employees.xlsx
+++ b/data/employees.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J1"/>
+  <dimension ref="A1:J3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -477,6 +477,102 @@
       <c r="J1" s="1" t="inlineStr">
         <is>
           <t>salary</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kiran Narhari Aglawe</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>RV001</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Development</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Intern</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>kiranaglawe2003@gmail.com</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>9766148444</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
+        <v>8000</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Avinash Ganesh Chate</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>RV002</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Development</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Intern</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>avinash@gmail.com</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>7058061264</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>3500</t>
         </is>
       </c>
     </row>
